--- a/survey_templates/038_sustainability_initiatives_implementation_assessment--survey_templates.xlsx
+++ b/survey_templates/038_sustainability_initiatives_implementation_assessment--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,9 +441,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,13 +525,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Organization Name</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What is the name of your organization?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please enter the name of your organization.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,10 +552,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>initiative_type</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Which type of sustainability initiative is this for?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Select one of the following options.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -571,10 +579,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>project_duration</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>How long has the project been going on?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Select one of the following options.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -594,10 +606,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>target_area</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Which areas does the initiative target?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Select all applicable areas.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -617,13 +633,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>budget</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>What budget is associated with the initiative?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please enter the budget amount.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -640,13 +660,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>expected_impact</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>What is the expected impact of the initiative?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please enter a number.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -663,13 +687,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>actual_impact</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>What is the actual impact of the initiative?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please enter a number.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -686,10 +714,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>sustainability_committee</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Is the organization's sustainability committee involved?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please answer with a yes or no.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -709,10 +741,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>greenhouse_gas</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Which type of greenhouse gas emissions are being addressed?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Select all applicable options.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -732,10 +768,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>carbon_offset</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>How much carbon offset is achieved through this initiative?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please enter a number.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -755,10 +795,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>water_conservation</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>What is the organization's water conservation rate?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please enter a number.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -778,10 +822,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>recycling_rate</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>What is the organization's recycling rate?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Select one of the following options.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -801,10 +849,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>transportation_mode</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Which mode of transportation is used for this initiative?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Select all applicable options.</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -824,10 +876,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>energy_efficiency</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>How energy efficient is this initiative?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Select one of the following options.</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>no</t>
@@ -847,10 +903,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>renewable_energy</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Which type of renewable energy is used?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Select all applicable options.</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
@@ -860,7 +920,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -870,10 +930,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>green_building</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Is the building certified as green?</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Please answer with a yes or no.</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
@@ -893,10 +957,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>green_certification</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Which green certification is obtained?</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Select all applicable options.</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>no</t>
@@ -916,10 +984,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>sustainable_water_sources</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Are there sustainable water sources used?</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Please answer with a yes or no.</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>no</t>
@@ -929,7 +1001,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -939,10 +1011,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>green_building_certification</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>Is the organization's building certified as green?</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Please answer with a yes or no.</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>no</t>
@@ -962,10 +1038,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>sustainable_land_use</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>How is the organization's land use managed sustainably?</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Please enter a description.</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>no</t>
@@ -980,15 +1060,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>transportation_mode</t>
+          <t>transportation_mode_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>transportation_mode</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>Which mode of transportation is used?</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Select all applicable options.</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>no</t>
@@ -1003,15 +1087,19 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>carbon_offset</t>
+          <t>carbon_offset_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>carbon_offset</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>How much carbon offset is achieved?</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Please enter a number.</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>no</t>
@@ -1026,15 +1114,19 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>green_building_certification</t>
+          <t>green_building_certification_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>green_building_certification</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>Green Building Certification 2</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Select all applicable options.</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>no</t>
@@ -1054,10 +1146,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>green_housekeeping</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>How is the organization's housekeeping managed sustainably?</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Please enter a description.</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>no</t>
@@ -1072,15 +1168,19 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>transportation_mode</t>
+          <t>transportation_mode_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>transportation_mode</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>Transportation Mode 3</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Select all applicable options.</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
@@ -1098,12 +1198,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1231,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'green_housekeeping'}</t>
+          <t>green_housekeeping</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Green Housekeeping'}</t>
+          <t>Green Housekeeping</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1248,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'green_purchasing'}</t>
+          <t>green_purchasing</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Green Purchasing'}</t>
+          <t>Green Purchasing</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1265,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'green_transportation'}</t>
+          <t>green_transportation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Green Transportation'}</t>
+          <t>Green Transportation</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1282,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'green_supply_chain'}</t>
+          <t>green_supply_chain</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Green Supply Chain'}</t>
+          <t>Green Supply Chain</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1299,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'less_than_6_months'}</t>
+          <t>less_than_6_months</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Less than 6 months'}</t>
+          <t>Less than 6 months</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1316,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'6-12_months'}</t>
+          <t>6-12_months</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '6-12 months'}</t>
+          <t>6-12 months</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1333,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'1-2_years'}</t>
+          <t>1-2_years</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '1-2 years'}</t>
+          <t>1-2 years</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1350,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'2-5_years'}</t>
+          <t>2-5_years</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': '2-5 years'}</t>
+          <t>2-5 years</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1367,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'more_than_5_years'}</t>
+          <t>more_than_5_years</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'More than 5 years'}</t>
+          <t>More than 5 years</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1384,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'community'}</t>
+          <t>community</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Community'}</t>
+          <t>Community</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1401,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'environment'}</t>
+          <t>environment</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Environment'}</t>
+          <t>Environment</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1418,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'employees'}</t>
+          <t>employees</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Employees'}</t>
+          <t>Employees</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1435,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'customers'}</t>
+          <t>customers</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Customers'}</t>
+          <t>Customers</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1452,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'electricity'}</t>
+          <t>electricity</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Electricity'}</t>
+          <t>Electricity</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1469,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'heat'}</t>
+          <t>heat</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Heat'}</t>
+          <t>Heat</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1486,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'water'}</t>
+          <t>water</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Water'}</t>
+          <t>Water</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1503,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'waste'}</t>
+          <t>waste</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Waste'}</t>
+          <t>Waste</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1520,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'0-10%'}</t>
+          <t>0-10%</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '0-10%'}</t>
+          <t>0-10%</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1537,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'11-20%'}</t>
+          <t>11-20%</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '11-20%'}</t>
+          <t>11-20%</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1554,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'21-30%'}</t>
+          <t>21-30%</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '21-30%'}</t>
+          <t>21-30%</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1571,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'31-40%'}</t>
+          <t>31-40%</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': '31-40%'}</t>
+          <t>31-40%</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1588,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'41-50%'}</t>
+          <t>41-50%</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': '41-50%'}</t>
+          <t>41-50%</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1605,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'drive'}</t>
+          <t>bike</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Drive'}</t>
+          <t>Bike</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1622,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'bus/rail'}</t>
+          <t>bus/rail</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Bus/Rail'}</t>
+          <t>Bus/Rail</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1639,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'walk/bycicle'}</t>
+          <t>car</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Walk/Bycicle'}</t>
+          <t>Car</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1656,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1673,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1690,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1707,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1724,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'solar'}</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Solar'}</t>
+          <t>Solar</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1741,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'wind'}</t>
+          <t>wind</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Wind'}</t>
+          <t>Wind</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1758,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'hydro'}</t>
+          <t>hydro</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Hydro'}</t>
+          <t>Hydro</t>
         </is>
       </c>
     </row>
@@ -1675,352 +1775,250 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>green_building_choices</t>
+          <t>green_certification_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'leed_certified'}</t>
+          <t>gbi</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Leed Certified'}</t>
+          <t>GBI</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>green_building_choices</t>
+          <t>green_certification_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'green_building_standard'}</t>
+          <t>leed</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Green Building Standard'}</t>
+          <t>LEED</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>green_building_choices</t>
+          <t>green_certification_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>green_certification_choices</t>
+          <t>transportation_mode_2_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'gbi'}</t>
+          <t>bus</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'GBI'}</t>
+          <t>Bus</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>green_certification_choices</t>
+          <t>transportation_mode_2_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'leed'}</t>
+          <t>walk/bycicle</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'LEED'}</t>
+          <t>Walk/Bycicle</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>green_certification_choices</t>
+          <t>transportation_mode_2_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>drive</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Drive</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>green_building_certification_choices</t>
+          <t>transportation_mode_2_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'gbi'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'GBI'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>green_building_certification_choices</t>
+          <t>green_building_certification_2_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'leed'}</t>
+          <t>gbi</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'LEED'}</t>
+          <t>GBI</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>green_building_certification_choices</t>
+          <t>green_building_certification_2_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>leed</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>LEED</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>transportation_mode_choices</t>
+          <t>green_building_certification_2_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'bike'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Bike'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>transportation_mode_choices</t>
+          <t>transportation_mode_3_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'bus/rail'}</t>
+          <t>bus</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Bus/Rail'}</t>
+          <t>Bus</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>transportation_mode_choices</t>
+          <t>transportation_mode_3_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'car'}</t>
+          <t>walk/bycicle</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Car'}</t>
+          <t>Walk/Bycicle</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>transportation_mode_choices</t>
+          <t>transportation_mode_3_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other'}</t>
+          <t>drive</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other'}</t>
+          <t>Drive</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>green_building_certification_choices</t>
+          <t>transportation_mode_3_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'gbi'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'GBI'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>green_building_certification_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_'leed'}</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': 'LEED'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>green_building_certification_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'label':_'other'}</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>transportation_mode_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_'bus'}</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': 'Bus'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>transportation_mode_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_'walk/bycicle'}</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': 'Walk/Bycicle'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>transportation_mode_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'label':_'drive'}</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'label': 'Drive'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>transportation_mode_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>{'id':_4,_'label':_'other'}</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>{'id': 4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
